--- a/src/test/resources/filters_professional_details/filters_role.xlsx
+++ b/src/test/resources/filters_professional_details/filters_role.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\Eticaa Project Automation\Eticaa-Automation\src\test\resources\filters_professional_details\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3495A58E-7191-4448-B587-8F10359E914D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F59ED53-E8A3-4A3B-A736-E6D7C4CDA1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Role" sheetId="1" r:id="rId1"/>
+    <sheet name="RoleFilters" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
